--- a/base_prov/ml/ml_abbott_2026-08-05.xlsx
+++ b/base_prov/ml/ml_abbott_2026-08-05.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\como se me cante\retail-chatbot-main\eci_abbott-main\base_prov\ml\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB121C72-9AD1-433B-BAD3-982E0219571E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3E5DCCB-578A-43F3-8E4B-05FAC7ECBC37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -461,9 +461,6 @@
     <t>https://www.mercadolibre.com.mx/pediasure-liquido-pack-16-piezas-237ml-fresa/p/MLM69626024?pdp_filters=shipping%3Afulfillment%7Cdeal%3AMLM1020488-1#polycard_client=search-desktop&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=4&amp;type=product&amp;tracking_id=6997a165-5eb2-4362-ba50-692a0187e98d&amp;wid=MLM5336513374&amp;sid=search</t>
   </si>
   <si>
-    <t>2026-08-04</t>
-  </si>
-  <si>
     <t>LECHE SIMILAC NEOSURE BEBES CON BAJO PESO 0 A 12 MESES 370G</t>
   </si>
   <si>
@@ -537,6 +534,9 @@
   </si>
   <si>
     <t>https://www.mercadolibre.com.mx/polvo-prosure-lata-sabor-vainilla-380g-abbott/p/MLM29693563</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
   </si>
 </sst>
 </file>
@@ -975,7 +975,7 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B2" t="s">
         <v>13</v>
@@ -1014,7 +1014,7 @@
         <v>362</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O2" t="s">
         <v>9</v>
@@ -1022,7 +1022,7 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
@@ -1037,7 +1037,7 @@
         <v>78</v>
       </c>
       <c r="F3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G3">
         <v>1000</v>
@@ -1061,7 +1061,7 @@
         <v>1227</v>
       </c>
       <c r="N3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O3" t="s">
         <v>11</v>
@@ -1069,7 +1069,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
@@ -1108,7 +1108,7 @@
         <v>1077</v>
       </c>
       <c r="N4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O4" t="s">
         <v>9</v>
@@ -1116,7 +1116,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
@@ -1155,7 +1155,7 @@
         <v>521</v>
       </c>
       <c r="N5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O5" t="s">
         <v>11</v>
@@ -1163,7 +1163,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
@@ -1202,7 +1202,7 @@
         <v>895</v>
       </c>
       <c r="N6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O6" t="s">
         <v>9</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -1249,7 +1249,7 @@
         <v>742</v>
       </c>
       <c r="N7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O7" t="s">
         <v>9</v>
@@ -1257,7 +1257,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -1296,7 +1296,7 @@
         <v>807</v>
       </c>
       <c r="N8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O8" t="s">
         <v>9</v>
@@ -1304,7 +1304,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -1343,7 +1343,7 @@
         <v>1182</v>
       </c>
       <c r="N9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O9" t="s">
         <v>9</v>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
@@ -1390,7 +1390,7 @@
         <v>756</v>
       </c>
       <c r="N10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="O10" t="s">
         <v>9</v>
@@ -1398,7 +1398,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
@@ -1437,7 +1437,7 @@
         <v>715</v>
       </c>
       <c r="N11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="O11" t="s">
         <v>9</v>
@@ -1445,7 +1445,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
@@ -1484,7 +1484,7 @@
         <v>944</v>
       </c>
       <c r="N12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O12" t="s">
         <v>9</v>
@@ -1492,7 +1492,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -1531,7 +1531,7 @@
         <v>805</v>
       </c>
       <c r="N13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O13" t="s">
         <v>9</v>
@@ -1539,7 +1539,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -1578,7 +1578,7 @@
         <v>792</v>
       </c>
       <c r="N14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O14" t="s">
         <v>9</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -1625,7 +1625,7 @@
         <v>1147</v>
       </c>
       <c r="N15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O15" t="s">
         <v>11</v>
@@ -1633,7 +1633,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
@@ -1680,7 +1680,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
@@ -1719,7 +1719,7 @@
         <v>479</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O17" t="s">
         <v>9</v>
@@ -1727,7 +1727,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
@@ -1766,7 +1766,7 @@
         <v>531</v>
       </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="O18" t="s">
         <v>9</v>
@@ -1774,7 +1774,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
@@ -1813,7 +1813,7 @@
         <v>1109</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O19" t="s">
         <v>9</v>
@@ -1821,7 +1821,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
@@ -1860,7 +1860,7 @@
         <v>1008</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O20" t="s">
         <v>9</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
@@ -1907,7 +1907,7 @@
         <v>1166</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O21" t="s">
         <v>9</v>
@@ -1915,7 +1915,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
@@ -1954,7 +1954,7 @@
         <v>783</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O22" t="s">
         <v>9</v>
@@ -1962,7 +1962,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
@@ -2009,7 +2009,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
@@ -2056,7 +2056,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B26" t="s">
         <v>13</v>
@@ -2150,7 +2150,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
@@ -2197,7 +2197,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B28" t="s">
         <v>13</v>
@@ -2244,7 +2244,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
@@ -2291,7 +2291,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B30" t="s">
         <v>13</v>
@@ -2338,7 +2338,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -2385,7 +2385,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B32" t="s">
         <v>13</v>
@@ -2432,7 +2432,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
@@ -2479,7 +2479,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
@@ -2526,7 +2526,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
@@ -2573,7 +2573,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B36" t="s">
         <v>13</v>
@@ -2620,7 +2620,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -2667,7 +2667,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -2714,7 +2714,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
@@ -2761,7 +2761,7 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
@@ -2808,7 +2808,7 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
@@ -2855,7 +2855,7 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -2902,7 +2902,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -2949,7 +2949,7 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B44" t="s">
         <v>13</v>
@@ -2996,7 +2996,7 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -3043,7 +3043,7 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B46" t="s">
         <v>13</v>
@@ -3090,7 +3090,7 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B47" t="s">
         <v>13</v>
@@ -3137,7 +3137,7 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
@@ -3184,7 +3184,7 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
@@ -3231,7 +3231,7 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B50" t="s">
         <v>13</v>
@@ -3278,7 +3278,7 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B51" t="s">
         <v>13</v>
@@ -3325,13 +3325,13 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
+        <v>166</v>
+      </c>
+      <c r="B52" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" t="s">
         <v>141</v>
-      </c>
-      <c r="B52" t="s">
-        <v>13</v>
-      </c>
-      <c r="C52" t="s">
-        <v>142</v>
       </c>
       <c r="D52">
         <v>1386166955</v>
@@ -3364,7 +3364,7 @@
         <v>1134</v>
       </c>
       <c r="N52" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O52" t="s">
         <v>9</v>
@@ -3372,7 +3372,7 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B53" t="s">
         <v>13</v>
@@ -3419,7 +3419,7 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -3466,7 +3466,7 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
@@ -3513,7 +3513,7 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B56" t="s">
         <v>13</v>
@@ -3560,7 +3560,7 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B57" t="s">
         <v>13</v>
@@ -3607,13 +3607,13 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
       </c>
       <c r="C58" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D58">
         <v>5507380358</v>
@@ -3654,7 +3654,7 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
@@ -3701,7 +3701,7 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -3748,7 +3748,7 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B61" t="s">
         <v>13</v>
@@ -3795,7 +3795,7 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -3842,7 +3842,7 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -3889,7 +3889,7 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
@@ -3936,7 +3936,7 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -3983,7 +3983,7 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B66" t="s">
         <v>13</v>
@@ -4030,13 +4030,13 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
       </c>
       <c r="C67" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D67">
         <v>2035768243</v>
@@ -4077,7 +4077,7 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B68" t="s">
         <v>13</v>
@@ -4124,7 +4124,7 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B69" t="s">
         <v>13</v>
@@ -4171,7 +4171,7 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B70" t="s">
         <v>13</v>
@@ -4218,7 +4218,7 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B71" t="s">
         <v>13</v>
@@ -4265,7 +4265,7 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
@@ -4312,7 +4312,7 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B73" t="s">
         <v>13</v>
@@ -4359,7 +4359,7 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B74" t="s">
         <v>13</v>
@@ -4406,7 +4406,7 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -4453,7 +4453,7 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B76" t="s">
         <v>13</v>
@@ -4500,7 +4500,7 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
@@ -4547,7 +4547,7 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B79" t="s">
         <v>13</v>
@@ -4641,7 +4641,7 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B80" t="s">
         <v>13</v>
